--- a/Timetable automate.xlsx
+++ b/Timetable automate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\TimeTable-Notifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2ACB9B-2733-461B-92A4-3B6F801C0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3407E790-D425-4648-A963-953F5919E9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Monday</t>
   </si>
@@ -51,21 +51,6 @@
     <t>Sunday</t>
   </si>
   <si>
-    <t>AI-L (8.30 - 9.50)</t>
-  </si>
-  <si>
-    <t>AI-L (10.00 - 11.20)</t>
-  </si>
-  <si>
-    <t>AI-L (11.30 - 12.50)</t>
-  </si>
-  <si>
-    <t>DS (8.30 - 9.50)</t>
-  </si>
-  <si>
-    <t>Arabic (10.00 - 11.20)</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -84,28 +69,55 @@
     <t>S3</t>
   </si>
   <si>
-    <t>Free (1.00 - 1.30)</t>
-  </si>
-  <si>
-    <t>SRE (1.30 - 3.00)</t>
-  </si>
-  <si>
     <t>S4</t>
   </si>
   <si>
-    <t>IM (3.00 - 4.30)</t>
-  </si>
-  <si>
-    <t>DS (10.00 - 11.20)</t>
-  </si>
-  <si>
-    <t>DS (11.30 - 12.50)</t>
-  </si>
-  <si>
-    <t>Arabuc (not confirm)</t>
-  </si>
-  <si>
-    <t>Entra (11.30 - 1.30)</t>
+    <t>Web Frameworks (3:50-5:10)</t>
+  </si>
+  <si>
+    <t>OS (2:30-3:50)</t>
+  </si>
+  <si>
+    <t>IS (9:50-11:10)</t>
+  </si>
+  <si>
+    <t>IS (11:10-12:30)</t>
+  </si>
+  <si>
+    <t>AOA 92:30-3:50) R10</t>
+  </si>
+  <si>
+    <t>Fehm ul Quran (11:10-12:30) R13</t>
+  </si>
+  <si>
+    <t>Web Frameworks (12:30-1:50) R13</t>
+  </si>
+  <si>
+    <t>Web  Frameworks (2:30-3:50) L2</t>
+  </si>
+  <si>
+    <t>Fehm ul Quran (8:30-9:50) R13</t>
+  </si>
+  <si>
+    <t>OS (10:30-12:30) R13</t>
+  </si>
+  <si>
+    <t>OS (12:30-1:50) L3</t>
+  </si>
+  <si>
+    <t>IS (8:30-9:50) L2</t>
+  </si>
+  <si>
+    <t>COAL (11:10-12:30) L3</t>
+  </si>
+  <si>
+    <t>COAL (12:30-1:50) L2</t>
+  </si>
+  <si>
+    <t>COAL ( 2:30-3:50) L2</t>
+  </si>
+  <si>
+    <t>AOA (3:50-5:10) R11</t>
   </si>
 </sst>
 </file>
@@ -491,25 +503,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -521,62 +533,68 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">

--- a/Timetable automate.xlsx
+++ b/Timetable automate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\TimeTable-Notifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3407E790-D425-4648-A963-953F5919E9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFE58D0-D17A-4CEB-B543-00115D5F040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,21 +72,6 @@
     <t>S4</t>
   </si>
   <si>
-    <t>Web Frameworks (3:50-5:10)</t>
-  </si>
-  <si>
-    <t>OS (2:30-3:50)</t>
-  </si>
-  <si>
-    <t>IS (9:50-11:10)</t>
-  </si>
-  <si>
-    <t>IS (11:10-12:30)</t>
-  </si>
-  <si>
-    <t>AOA 92:30-3:50) R10</t>
-  </si>
-  <si>
     <t>Fehm ul Quran (11:10-12:30) R13</t>
   </si>
   <si>
@@ -118,6 +103,21 @@
   </si>
   <si>
     <t>AOA (3:50-5:10) R11</t>
+  </si>
+  <si>
+    <t>AOA (2:30-3:50) R10</t>
+  </si>
+  <si>
+    <t>Web Frameworks (3:50-5:10) L2</t>
+  </si>
+  <si>
+    <t>OS (2:30-3:50) L3</t>
+  </si>
+  <si>
+    <t>IS (9:50-11:10) L2</t>
+  </si>
+  <si>
+    <t>IS (11:10-12:30) L2</t>
   </si>
 </sst>
 </file>
@@ -534,16 +534,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -551,16 +551,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -568,16 +568,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -585,16 +585,16 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">

--- a/Timetable automate.xlsx
+++ b/Timetable automate.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFE58D0-D17A-4CEB-B543-00115D5F040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Timetable automate.xlsx
+++ b/Timetable automate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\TimeTable-Notifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFE58D0-D17A-4CEB-B543-00115D5F040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36143FEA-9F77-4973-96C0-0F7C4B5EB2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Monday</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>IS (11:10-12:30) L2</t>
+  </si>
+  <si>
+    <t>S5</t>
   </si>
 </sst>
 </file>
@@ -179,9 +182,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9D9F75D2-973F-409D-8A64-A38B1655872B}" name="Table2" displayName="Table2" ref="A1:H10" totalsRowShown="0">
-  <autoFilter ref="A1:H10" xr:uid="{9D9F75D2-973F-409D-8A64-A38B1655872B}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9D9F75D2-973F-409D-8A64-A38B1655872B}" name="Table2" displayName="Table2" ref="A1:I10" totalsRowShown="0">
+  <autoFilter ref="A1:I10" xr:uid="{9D9F75D2-973F-409D-8A64-A38B1655872B}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{20729885-ACEF-4328-9F57-AE0BA1A03AFD}" name="Day"/>
     <tableColumn id="2" xr3:uid="{C8313110-FDA1-4BF8-9BEA-9ECCF2549B73}" name="C"/>
     <tableColumn id="3" xr3:uid="{00508CD3-629A-466F-8AA7-C9B18E8D387C}" name="L"/>
@@ -190,6 +193,7 @@
     <tableColumn id="6" xr3:uid="{8B25BFCB-F4B8-4CEE-B5E7-35C622E7CEEC}" name="E"/>
     <tableColumn id="7" xr3:uid="{5A987935-F8DB-4724-92AE-C7799D111A1D}" name="S3"/>
     <tableColumn id="8" xr3:uid="{229B01B7-206B-40BF-9F06-D1A5198A0218}" name="S4"/>
+    <tableColumn id="9" xr3:uid="{454A596B-1CDA-46A4-A98F-B496715A1ACA}" name="S5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -492,13 +496,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3DBC07-9203-49C2-9FBE-129073047257}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -523,13 +527,16 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -546,7 +553,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -563,7 +570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -580,7 +587,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -597,17 +604,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>

--- a/Timetable automate.xlsx
+++ b/Timetable automate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\TimeTable-Notifier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36143FEA-9F77-4973-96C0-0F7C4B5EB2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97860BF-7275-4201-B7B3-BF7398AC4BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{14E72CCB-0E79-4B7E-BD78-A2B34D426CDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t>COAL ( 2:30-3:50) L2</t>
   </si>
   <si>
-    <t>AOA (3:50-5:10) R11</t>
-  </si>
-  <si>
     <t>AOA (2:30-3:50) R10</t>
   </si>
   <si>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t>S5</t>
+  </si>
+  <si>
+    <t>AOA (9:50 - 11:10 )</t>
   </si>
 </sst>
 </file>
@@ -528,7 +528,7 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -540,6 +540,9 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
@@ -550,7 +553,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -567,7 +570,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -578,13 +581,13 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -599,9 +602,6 @@
       </c>
       <c r="F6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
